--- a/data/trans_bre/P6904-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P6904-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-34,01; 2,47</t>
+          <t>-34,59; 1,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-27,27; 14,92</t>
+          <t>-28,25; 13,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,43; 31,05</t>
+          <t>-20,27; 31,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-24,32; 22,7</t>
+          <t>-23,2; 21,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-45,51; 3,1</t>
+          <t>-45,21; 2,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-40,36; 31,33</t>
+          <t>-41,1; 25,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-32,73; 68,56</t>
+          <t>-34,45; 67,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-29,01; 35,59</t>
+          <t>-28,72; 34,19</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 19,26</t>
+          <t>-2,6; 18,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 13,2</t>
+          <t>-9,4; 13,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 20,01</t>
+          <t>0,66; 20,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 22,69</t>
+          <t>-2,51; 19,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 41,86</t>
+          <t>-4,88; 39,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-15,21; 25,35</t>
+          <t>-15,73; 25,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 34,59</t>
+          <t>0,92; 35,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 39,53</t>
+          <t>-3,76; 35,42</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,2; 22,9</t>
+          <t>-9,88; 23,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-31,15; 12,18</t>
+          <t>-31,37; 10,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,55; 26,07</t>
+          <t>-9,44; 26,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,32; 15,72</t>
+          <t>-17,95; 17,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-30,55; 106,52</t>
+          <t>-27,31; 113,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-61,81; 44,71</t>
+          <t>-62,22; 39,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-17,81; 66,29</t>
+          <t>-17,44; 65,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-28,9; 38,72</t>
+          <t>-28,8; 43,43</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 7,74</t>
+          <t>-8,75; 8,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 5,94</t>
+          <t>-12,39; 4,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 16,7</t>
+          <t>-0,46; 16,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 14,81</t>
+          <t>-3,81; 15,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-16,13; 15,39</t>
+          <t>-15,95; 17,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,29; 11,74</t>
+          <t>-21,38; 9,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 29,81</t>
+          <t>-0,77; 30,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 26,47</t>
+          <t>-5,95; 28,2</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P6904-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P6904-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,66</t>
+          <t>-11,34</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-2,16%</t>
+          <t>-14,15%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-34,59; 1,86</t>
+          <t>-34,83; 1,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-28,25; 13,24</t>
+          <t>-25,87; 16,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-20,27; 31,83</t>
+          <t>-21,37; 29,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-23,2; 21,48</t>
+          <t>-31,25; 10,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-45,21; 2,7</t>
+          <t>-46,97; 1,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-41,1; 25,21</t>
+          <t>-40,57; 33,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-34,45; 67,3</t>
+          <t>-31,8; 68,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-28,72; 34,19</t>
+          <t>-36,61; 13,03</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,69</t>
+          <t>0,04</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>0,05%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 18,51</t>
+          <t>-2,56; 19,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 13,34</t>
+          <t>-9,36; 13,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 20,47</t>
+          <t>0,47; 19,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 19,88</t>
+          <t>-9,28; 8,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 39,92</t>
+          <t>-4,9; 42,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-15,73; 25,22</t>
+          <t>-15,6; 25,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 35,1</t>
+          <t>0,85; 33,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 35,42</t>
+          <t>-13,69; 14,31</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,52</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-2,89%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,88; 23,91</t>
+          <t>-10,72; 22,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-31,37; 10,56</t>
+          <t>-32,84; 10,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,44; 26,14</t>
+          <t>-10,36; 25,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,95; 17,23</t>
+          <t>-17,66; 16,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-27,31; 113,7</t>
+          <t>-30,55; 97,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-62,22; 39,49</t>
+          <t>-62,53; 36,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-17,44; 65,52</t>
+          <t>-17,24; 66,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-28,8; 43,43</t>
+          <t>-28,52; 42,45</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,96</t>
+          <t>-2,09</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>-3,3%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 8,36</t>
+          <t>-8,72; 7,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 4,87</t>
+          <t>-12,03; 5,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 16,95</t>
+          <t>-1,07; 15,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 15,67</t>
+          <t>-9,52; 4,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-15,95; 17,22</t>
+          <t>-15,42; 15,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-21,38; 9,84</t>
+          <t>-21,06; 11,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 30,6</t>
+          <t>-1,81; 28,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 28,2</t>
+          <t>-13,86; 8,47</t>
         </is>
       </c>
     </row>
